--- a/input_data/intervention_designs.xlsx
+++ b/input_data/intervention_designs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominicbuettiker/Documents/GitHub/Parametric-LCA-Urban-Densification/input_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC14841-6D0B-C845-BEA3-FB55A641D2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39BE4BD-EE5C-FA4F-A6FA-69E01661D6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17920" xr2:uid="{88AF4FB5-E207-2C48-AD3B-42156AB0748F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2190" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2265" uniqueCount="115">
   <si>
     <t>scenario</t>
   </si>
@@ -357,6 +357,30 @@
   </si>
   <si>
     <t>same_interventions_on_all_2</t>
+  </si>
+  <si>
+    <t>model_validation_eren4</t>
+  </si>
+  <si>
+    <t>eRen4</t>
+  </si>
+  <si>
+    <t>Natural Gas old</t>
+  </si>
+  <si>
+    <t>radiator old</t>
+  </si>
+  <si>
+    <t>hydronic old</t>
+  </si>
+  <si>
+    <t>conventional_deep_ren</t>
+  </si>
+  <si>
+    <t>eps</t>
+  </si>
+  <si>
+    <t>bio_optimal_ren</t>
   </si>
 </sst>
 </file>
@@ -748,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F55BA4-0E8D-A046-8D35-585DD3A28B87}">
-  <dimension ref="A1:AC104"/>
+  <dimension ref="A1:AC110"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.5" customWidth="1"/>
@@ -8888,6 +8912,274 @@
         <v>33</v>
       </c>
     </row>
+    <row r="106" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="108" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C108" s="1">
+        <v>1</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K108" s="1">
+        <v>0</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M108" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O108" s="1">
+        <v>0</v>
+      </c>
+      <c r="P108" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q108" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="R108" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S108" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="T108" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U108" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="V108" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="W108" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X108" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y108" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z108" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="AA108" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB108" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC108" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="109" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C109" s="1">
+        <v>1</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="K109" s="1">
+        <v>24</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M109" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N109" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O109" s="1">
+        <v>0</v>
+      </c>
+      <c r="P109" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q109" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="R109" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S109" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="T109" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U109" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="V109" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="W109" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X109" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y109" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z109" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="AA109" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB109" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC109" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="110" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C110" s="1">
+        <v>1</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K110" s="1">
+        <v>64</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M110" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N110" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O110" s="1">
+        <v>0</v>
+      </c>
+      <c r="P110" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q110" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="R110" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S110" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T110" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U110" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="V110" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W110" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X110" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y110" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z110" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="AA110" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB110" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC110" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
